--- a/reports/20260507/BulkStatusChange_claude.xlsx
+++ b/reports/20260507/BulkStatusChange_claude.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,12 +37,8 @@
       <b val="1"/>
       <color rgb="00276221"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +86,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -569,7 +557,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1761</t>
+          <t>candidateId=1803</t>
         </is>
       </c>
     </row>
@@ -616,7 +604,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1763</t>
+          <t>candidateId=1807</t>
         </is>
       </c>
     </row>
@@ -663,7 +651,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1767</t>
+          <t>candidateId=1813</t>
         </is>
       </c>
     </row>
@@ -804,7 +792,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>ContextId=4ee3aa00-a05f-405e-baf9-d2487740696b</t>
+          <t>ContextId=d2f9dbc2-4709-4a62-9b3f-cc9f01222080</t>
         </is>
       </c>
     </row>
@@ -831,7 +819,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Poll /py/crpo/api/v1/getStatusOfAsyncAPI with ContextId 4ee3aa00-a05f-405e-baf9-d2487740696b.</t>
+          <t>Poll /py/crpo/api/v1/getStatusOfAsyncAPI with ContextId d2f9dbc2-4709-4a62-9b3f-cc9f01222080.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -844,14 +832,14 @@
           <t>JobState matches 'SUCCESS' or 'OK' within 60 seconds.</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>final state=TIMEOUT</t>
+          <t>final state=SUCCESS</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1591,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403, xss_reflected=False</t>
+          <t>HTTP 200, xss_reflected=False</t>
         </is>
       </c>
     </row>
@@ -1643,14 +1631,14 @@
           <t>Elapsed time &lt; 30s and no HTTP 500.</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>HTTP 403, status=None, elapsed=0.1s</t>
+          <t>HTTP 200, status=KO, elapsed=0.2s</t>
         </is>
       </c>
     </row>
